--- a/PCB/PlanDeTest.xlsx
+++ b/PCB/PlanDeTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\royza\Desktop\Labo\CircuitImprimé\SuperStyleTheGoodOne\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A873C1A6-F45D-40E3-AB10-210161622359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E68ADA-94DF-478E-9529-F1034425A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -126,12 +126,6 @@
     <t>Dans V1, la trace entre les deux est rated 0.8A. J'ai dût mettre un fil pour que ça marche</t>
   </si>
   <si>
-    <t>Tester la résistance entre le testpoint 12V et GND. Elle devrait être dans les mégaohms</t>
-  </si>
-  <si>
-    <t>Tester la résistance entre le testpoint VDD et GND. Elle devrait être dans les mégaohms</t>
-  </si>
-  <si>
     <t>Avec un multimètre, tester les bouttons S1,S2,S3. S1 est pull-down, S2,S3 sont pull-up</t>
   </si>
   <si>
@@ -142,6 +136,30 @@
   </si>
   <si>
     <t>Pousser le code.</t>
+  </si>
+  <si>
+    <t>Tester la résistance entre le testpoint VDD et GND. Elle devrait être dans les kohm</t>
+  </si>
+  <si>
+    <t>Plusieur composante sont soit trop petite ou trop grosse pour leur traces</t>
+  </si>
+  <si>
+    <t>J'ai utilisé des fils pour les connecter</t>
+  </si>
+  <si>
+    <t>Tester la résistance entre le testpoint 12V et GND. Elle devrait être dans les Kohm</t>
+  </si>
+  <si>
+    <t>3.8 Kohm</t>
+  </si>
+  <si>
+    <t>J'ai 40 Kohm</t>
+  </si>
+  <si>
+    <t>On a seulement le boutton S2 à cause que les traces sont plus petite que les bouttons</t>
+  </si>
+  <si>
+    <t>Aucun</t>
   </si>
 </sst>
 </file>
@@ -354,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -417,9 +435,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1208,17 +1223,25 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+      <c r="D11" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>1</v>
+      </c>
       <c r="H11" s="18"/>
     </row>
     <row r="12" spans="2:10" ht="38" customHeight="1" x14ac:dyDescent="0.35">
@@ -1226,10 +1249,14 @@
         <v>10</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="18"/>
+        <v>36</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>38</v>
+      </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
@@ -1239,10 +1266,14 @@
         <v>10</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="18"/>
+        <v>33</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>37</v>
+      </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
@@ -1252,12 +1283,20 @@
         <v>11</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
+        <v>29</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>1</v>
+      </c>
       <c r="H14" s="18"/>
     </row>
     <row r="15" spans="2:10" ht="29" x14ac:dyDescent="0.35">
@@ -1265,7 +1304,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="18"/>
@@ -1277,8 +1316,8 @@
       <c r="B16" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="29" t="s">
-        <v>33</v>
+      <c r="C16" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="24"/>
@@ -1291,7 +1330,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D17" s="16"/>
       <c r="E17" s="18"/>
@@ -1690,18 +1729,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1849,18 +1888,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/PCB/PlanDeTest.xlsx
+++ b/PCB/PlanDeTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\royza\Desktop\Labo\CircuitImprimé\SuperStyleTheGoodOne\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E68ADA-94DF-478E-9529-F1034425A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC0E552-B4D6-43A8-AB90-4BBDF5DBCE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Aucun</t>
+  </si>
+  <si>
+    <t>Avec le code, voir si le STM voie les communication UART du controlleur</t>
   </si>
 </sst>
 </file>
@@ -1339,8 +1342,12 @@
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="1"/>
-      <c r="C18" s="15"/>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="D18" s="16"/>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>

--- a/PCB/PlanDeTest.xlsx
+++ b/PCB/PlanDeTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\royza\Desktop\Labo\CircuitImprimé\SuperStyleTheGoodOne\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC0E552-B4D6-43A8-AB90-4BBDF5DBCE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E67A246-5A44-40AA-BF0B-43A788BDC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -159,10 +159,13 @@
     <t>On a seulement le boutton S2 à cause que les traces sont plus petite que les bouttons</t>
   </si>
   <si>
-    <t>Aucun</t>
-  </si>
-  <si>
     <t>Avec le code, voir si le STM voie les communication UART du controlleur</t>
+  </si>
+  <si>
+    <t>Seulement la diode D2 allume</t>
+  </si>
+  <si>
+    <t>Aucune</t>
   </si>
 </sst>
 </file>
@@ -375,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -424,9 +427,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -438,6 +438,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1119,7 +1134,7 @@
     <row r="1" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="25" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="3"/>
@@ -1127,12 +1142,12 @@
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="5"/>
-      <c r="C3" s="27"/>
+      <c r="C3" s="26"/>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="2:10" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="5"/>
-      <c r="C4" s="28"/>
+      <c r="C4" s="27"/>
       <c r="E4" s="6"/>
       <c r="J4" t="s">
         <v>1</v>
@@ -1281,82 +1296,84 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="2:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="B14" s="1" t="s">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+    </row>
+    <row r="16" spans="2:10" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C16" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E16" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="18" t="s">
+      <c r="F16" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="2:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="B15" s="1" t="s">
+      <c r="H16" s="31"/>
+    </row>
+    <row r="17" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C17" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-    </row>
-    <row r="16" spans="2:10" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="15" t="s">
+      <c r="D17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+    </row>
+    <row r="18" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C18" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="1" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+    </row>
+    <row r="19" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C19" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="1"/>
-      <c r="C19" s="15"/>
       <c r="D19" s="16"/>
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
@@ -1364,8 +1381,12 @@
       <c r="H19" s="18"/>
     </row>
     <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="B20" s="1"/>
-      <c r="C20" s="15"/>
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>40</v>
+      </c>
       <c r="D20" s="16"/>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -1402,7 +1423,7 @@
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
       <c r="C24" s="15"/>
-      <c r="D24" s="25"/>
+      <c r="D24" s="24"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
@@ -1487,12 +1508,12 @@
     <mergeCell ref="C2:C4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D11:D23 G11:G23">
+  <conditionalFormatting sqref="D11:D13 D16:D23 G11:G13 G16:G23">
     <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Échec">
       <formula>NOT(ISERROR(SEARCH("Échec",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:H23">
+  <conditionalFormatting sqref="F11:H13 F16:H23">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$D11=""</formula>
     </cfRule>
@@ -1500,16 +1521,16 @@
       <formula>$D11="Réussi"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G23 D11:D23">
+  <conditionalFormatting sqref="G11:G13 G16:G23 D11:D13 D16:D23">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Réussi">
       <formula>NOT(ISERROR(SEARCH("Réussi",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G23 D11:D23" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G13 D11:D13 D16:D23 G16:G23" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
       <formula1>$J$4:$J$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:B23" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B16:B23" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
       <formula1>$J$8:$J$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -1736,18 +1757,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1895,18 +1916,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/PCB/PlanDeTest.xlsx
+++ b/PCB/PlanDeTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\royza\Desktop\Labo\CircuitImprimé\SuperStyleTheGoodOne\PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E67A246-5A44-40AA-BF0B-43A788BDC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13661EA8-56CB-4E0B-9817-D2AB71BFF936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -166,6 +166,69 @@
   </si>
   <si>
     <t>Aucune</t>
+  </si>
+  <si>
+    <t>Assemblé le boitier avec le PCB</t>
+  </si>
+  <si>
+    <t>les trous trop éloigner</t>
+  </si>
+  <si>
+    <t>Une version 2 du boititer est faite</t>
+  </si>
+  <si>
+    <t>Il s'assemble bien</t>
+  </si>
+  <si>
+    <t>Le connecteur est flipé</t>
+  </si>
+  <si>
+    <t>Prière a zeus</t>
+  </si>
+  <si>
+    <t>Tristess et désolation</t>
+  </si>
+  <si>
+    <t>Le régulateur en fonctionne pas. On a branché un fil au 3V3</t>
+  </si>
+  <si>
+    <t>On a une alimentation 3V3, mais notre 12V est devenue 2.5V. Les deux lumières allume</t>
+  </si>
+  <si>
+    <t>Incapable de détecté le MCU part le port USB-C</t>
+  </si>
+  <si>
+    <t>Ajouté un fil pour mettre ne mode boot</t>
+  </si>
+  <si>
+    <t>On ne détecte pas encore le MCU</t>
+  </si>
+  <si>
+    <t>Avec le code, voir les valeur du IMU</t>
+  </si>
+  <si>
+    <t>Il manque la librairie CustomTk</t>
+  </si>
+  <si>
+    <t>Enlever la librairie CustomTk du code</t>
+  </si>
+  <si>
+    <t>Le code execute</t>
+  </si>
+  <si>
+    <t>Bouger le PCB toute en lisant la pin GPIO21. Elle devrait changer quand le pcb bouge brusquement</t>
+  </si>
+  <si>
+    <t>Sur le raspberryPI, executer le code .PY</t>
+  </si>
+  <si>
+    <t>Connecter le PCB au RaspberryPI. Le PI doit commencer a détecter des données sur le port UART</t>
+  </si>
+  <si>
+    <t>On est incapable de pousser le code dans le STM32</t>
+  </si>
+  <si>
+    <t>L'affichage du RaspberryPI affiche les données de la trotinette</t>
   </si>
 </sst>
 </file>
@@ -378,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -445,9 +508,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -458,7 +518,33 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="20">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -790,25 +876,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H24" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="B10:H24" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H26" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17">
+  <autoFilter ref="B10:H26" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{46119054-E687-474D-A236-70842A202FA2}" name="Résultat" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{E76DCA99-A14D-4F97-96AC-0659630D86A5}" name="Raison réussite ou échec" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{C0DEE3AC-0260-44EA-839D-A616D9FF1BF7}" name="modification effectuée" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{EB8F3DD3-BA06-4471-97FB-7FC066A8F5DD}" name="Nouveau résultat" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{853C2233-5CDD-4625-B476-83FD3F9762B1}" name="Commentaire" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{46119054-E687-474D-A236-70842A202FA2}" name="Résultat" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{E76DCA99-A14D-4F97-96AC-0659630D86A5}" name="Raison réussite ou échec" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{C0DEE3AC-0260-44EA-839D-A616D9FF1BF7}" name="modification effectuée" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{EB8F3DD3-BA06-4471-97FB-7FC066A8F5DD}" name="Nouveau résultat" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{853C2233-5CDD-4625-B476-83FD3F9762B1}" name="Commentaire" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}" name="Table38" displayName="Table38" ref="B2:D15" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}" name="Table38" displayName="Table38" ref="B2:D15" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" dataCellStyle="Normal">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D8886178-DA38-4DAF-A779-65758840ADDA}" name="#" dataDxfId="4" dataCellStyle="Normal">
+    <tableColumn id="1" xr3:uid="{D8886178-DA38-4DAF-A779-65758840ADDA}" name="#" dataDxfId="6" dataCellStyle="Normal">
       <calculatedColumnFormula>B2+1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F83C734D-9C3E-4041-9C4C-0512ABCBDEB0}" name="Modification suggérée" dataCellStyle="Normal"/>
@@ -1118,7 +1204,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:J42"/>
+  <dimension ref="B1:J44"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1296,159 +1382,253 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B14" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-    </row>
-    <row r="16" spans="2:10" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="47.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="30"/>
+    </row>
+    <row r="16" spans="2:10" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="31"/>
+      <c r="E16" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="17" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="28" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>4</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
+        <v>47</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-    </row>
-    <row r="19" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="21" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="18"/>
+        <v>40</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>62</v>
+      </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
     </row>
-    <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="18"/>
+        <v>55</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>62</v>
+      </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
     </row>
     <row r="21" spans="2:8" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="1"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
+      <c r="B21" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
     </row>
     <row r="22" spans="2:8" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="1"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
+      <c r="B22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="23" spans="2:8" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="1"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="18"/>
+      <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>62</v>
+      </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="1"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B30" s="19"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="20"/>
+    <row r="24" spans="2:8" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+    </row>
+    <row r="25" spans="2:8" ht="53.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B31" s="19"/>
-      <c r="C31" s="20"/>
+      <c r="B31" s="20"/>
       <c r="D31" s="20"/>
       <c r="E31" s="20"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B32" s="19"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="20"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.35">
@@ -1469,7 +1649,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
     </row>
-    <row r="36" spans="2:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="19"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
@@ -1481,7 +1661,7 @@
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:5" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="19"/>
       <c r="C38" s="20"/>
       <c r="D38" s="20"/>
@@ -1489,11 +1669,15 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39" s="19"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40" s="19"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="19"/>
@@ -1502,35 +1686,51 @@
     <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42" s="19"/>
       <c r="D42" s="20"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B43" s="19"/>
+      <c r="D43" s="20"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B44" s="19"/>
+      <c r="D44" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:C4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D11:D13 D16:D23 G11:G13 G16:G23">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Échec">
+  <conditionalFormatting sqref="D11:D25 G11:G25">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Échec">
       <formula>NOT(ISERROR(SEARCH("Échec",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:H13 F16:H23">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="F11:H13 F15:H25">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>$D11=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$D11="Réussi"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G13 G16:G23 D11:D13 D16:D23">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Réussi">
+  <conditionalFormatting sqref="D11:D25 G11:G25">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Réussi">
       <formula>NOT(ISERROR(SEARCH("Réussi",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$D14=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$D14="Réussi"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G13 D11:D13 D16:D23 G16:G23" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G25 D11:D25" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
       <formula1>$J$4:$J$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B16:B23" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13 B15:B25" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
       <formula1>$J$8:$J$10</formula1>
     </dataValidation>
   </dataValidations>
